--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11577,6 +11577,87 @@
       <c r="G413" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="C414" t="n">
+        <v>282.52</v>
+      </c>
+      <c r="D414" t="n">
+        <v>302.16</v>
+      </c>
+      <c r="E414" t="n">
+        <v>297.02</v>
+      </c>
+      <c r="F414" t="n">
+        <v>304.46</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>292.79</v>
+      </c>
+      <c r="C415" t="n">
+        <v>283.29</v>
+      </c>
+      <c r="D415" t="n">
+        <v>301.86</v>
+      </c>
+      <c r="E415" t="n">
+        <v>296.81</v>
+      </c>
+      <c r="F415" t="n">
+        <v>304.56</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>293.36</v>
+      </c>
+      <c r="C416" t="n">
+        <v>283.19</v>
+      </c>
+      <c r="D416" t="n">
+        <v>300.69</v>
+      </c>
+      <c r="E416" t="n">
+        <v>295.98</v>
+      </c>
+      <c r="F416" t="n">
+        <v>304.4</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16204,6 +16285,36 @@
       </c>
       <c r="B461" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -16372,28 +16483,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2662888444510006</v>
+        <v>-0.2763426569796371</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01634225275724044</v>
+        <v>0.01780039247960019</v>
       </c>
       <c r="M2" t="n">
-        <v>12.82404141578175</v>
+        <v>12.78319699966808</v>
       </c>
       <c r="N2" t="n">
-        <v>219.6250604866343</v>
+        <v>218.3793267193232</v>
       </c>
       <c r="O2" t="n">
-        <v>14.81975237602283</v>
+        <v>14.77766310075186</v>
       </c>
       <c r="P2" t="n">
-        <v>306.8183245537119</v>
+        <v>306.9298720959126</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16454,28 +16565,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5458684377960421</v>
+        <v>-0.5562610983085585</v>
       </c>
       <c r="J3" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05412966243213158</v>
+        <v>0.05678693263401569</v>
       </c>
       <c r="M3" t="n">
-        <v>13.63865620748129</v>
+        <v>13.59386826113606</v>
       </c>
       <c r="N3" t="n">
-        <v>268.8246213923136</v>
+        <v>267.2630579479263</v>
       </c>
       <c r="O3" t="n">
-        <v>16.39587208392142</v>
+        <v>16.34818209917929</v>
       </c>
       <c r="P3" t="n">
-        <v>304.7367645452127</v>
+        <v>304.8515928051953</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16536,28 +16647,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7068325350190663</v>
+        <v>-0.7138394901700068</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K4" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4090706998024251</v>
+        <v>0.4162005162826401</v>
       </c>
       <c r="M4" t="n">
-        <v>4.882086796982993</v>
+        <v>4.884391766363207</v>
       </c>
       <c r="N4" t="n">
-        <v>37.21909824486717</v>
+        <v>37.12756828840575</v>
       </c>
       <c r="O4" t="n">
-        <v>6.100745712195122</v>
+        <v>6.093239556131512</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1329807562794</v>
+        <v>325.2104066400446</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16614,28 +16725,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5200658422987364</v>
+        <v>-0.5335274325436179</v>
       </c>
       <c r="J5" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K5" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3180317007578134</v>
+        <v>0.327661388008702</v>
       </c>
       <c r="M5" t="n">
-        <v>4.46963189062178</v>
+        <v>4.526962171499703</v>
       </c>
       <c r="N5" t="n">
-        <v>29.90928764401431</v>
+        <v>30.33965023102641</v>
       </c>
       <c r="O5" t="n">
-        <v>5.468938438491907</v>
+        <v>5.508143991493542</v>
       </c>
       <c r="P5" t="n">
-        <v>319.8361840590554</v>
+        <v>319.9849237390951</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16692,28 +16803,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3610053808813697</v>
+        <v>-0.3787188083082204</v>
       </c>
       <c r="J6" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1787096807996483</v>
+        <v>0.1899063359010292</v>
       </c>
       <c r="M6" t="n">
-        <v>4.420991803751441</v>
+        <v>4.483045439031582</v>
       </c>
       <c r="N6" t="n">
-        <v>30.88670698719246</v>
+        <v>31.78072519474607</v>
       </c>
       <c r="O6" t="n">
-        <v>5.557581037393199</v>
+        <v>5.637439595662739</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5404424454368</v>
+        <v>326.7361547362659</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16751,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32011,6 +32122,117 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-45.12192960748595,170.98046503615632</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-45.122207955358604,170.9795850834272</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-45.122799074150066,170.9790128908403</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-45.12322461541653,170.97831387271344</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-45.1237402075041,170.97776234170473</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-45.121935436311595,170.9804698420753</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-45.12221359772714,170.97959076463798</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-45.12279707694787,170.9790103250895</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-45.12322327922143,170.9783119850824</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-45.12374083167914,170.97776325736652</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-45.12193986621896,170.9804734945744</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-45.12221286495202,170.97959002681833</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-45.122789287858744,170.97900031866303</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-45.12321799806905,170.9783045244463</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-45.12373983299908,170.97776179230766</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G416"/>
+  <dimension ref="A1:G418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11656,6 +11656,60 @@
         <v>304.4</v>
       </c>
       <c r="G416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>301.34</v>
+      </c>
+      <c r="C417" t="n">
+        <v>291.19</v>
+      </c>
+      <c r="D417" t="n">
+        <v>300.27</v>
+      </c>
+      <c r="E417" t="n">
+        <v>295.78</v>
+      </c>
+      <c r="F417" t="n">
+        <v>303.41</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>301.28</v>
+      </c>
+      <c r="C418" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="D418" t="n">
+        <v>298.74</v>
+      </c>
+      <c r="E418" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="F418" t="n">
+        <v>301.06</v>
+      </c>
+      <c r="G418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11672,7 +11726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B464"/>
+  <dimension ref="A1:B466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16315,6 +16369,26 @@
       </c>
       <c r="B464" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -16483,28 +16557,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2763426569796371</v>
+        <v>-0.2747091125495743</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01780039247960019</v>
+        <v>0.01776438337765773</v>
       </c>
       <c r="M2" t="n">
-        <v>12.78319699966808</v>
+        <v>12.72912104236963</v>
       </c>
       <c r="N2" t="n">
-        <v>218.3793267193232</v>
+        <v>217.3332620849215</v>
       </c>
       <c r="O2" t="n">
-        <v>14.77766310075186</v>
+        <v>14.74222717519037</v>
       </c>
       <c r="P2" t="n">
-        <v>306.9298720959126</v>
+        <v>306.9115585740059</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16565,28 +16639,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5562610983085585</v>
+        <v>-0.5553773353043716</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05678693263401569</v>
+        <v>0.05714411402490593</v>
       </c>
       <c r="M3" t="n">
-        <v>13.59386826113606</v>
+        <v>13.53290111815487</v>
       </c>
       <c r="N3" t="n">
-        <v>267.2630579479263</v>
+        <v>265.9823960488398</v>
       </c>
       <c r="O3" t="n">
-        <v>16.34818209917929</v>
+        <v>16.30896673762136</v>
       </c>
       <c r="P3" t="n">
-        <v>304.8515928051953</v>
+        <v>304.841727645492</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16647,28 +16721,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7138394901700068</v>
+        <v>-0.7202455384361239</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4162005162826401</v>
+        <v>0.4215106244729381</v>
       </c>
       <c r="M4" t="n">
-        <v>4.884391766363207</v>
+        <v>4.895947319141836</v>
       </c>
       <c r="N4" t="n">
-        <v>37.12756828840575</v>
+        <v>37.16849336266782</v>
       </c>
       <c r="O4" t="n">
-        <v>6.093239556131512</v>
+        <v>6.096596867324247</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2104066400446</v>
+        <v>325.2819191881263</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16725,28 +16799,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5335274325436179</v>
+        <v>-0.5442023444277596</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.327661388008702</v>
+        <v>0.334205003140432</v>
       </c>
       <c r="M5" t="n">
-        <v>4.526962171499703</v>
+        <v>4.575018439258449</v>
       </c>
       <c r="N5" t="n">
-        <v>30.33965023102641</v>
+        <v>30.80174629335026</v>
       </c>
       <c r="O5" t="n">
-        <v>5.508143991493542</v>
+        <v>5.549932098084648</v>
       </c>
       <c r="P5" t="n">
-        <v>319.9849237390951</v>
+        <v>320.1040906159649</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16803,28 +16877,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3787188083082204</v>
+        <v>-0.3924073235028762</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1899063359010292</v>
+        <v>0.1977060903401522</v>
       </c>
       <c r="M6" t="n">
-        <v>4.483045439031582</v>
+        <v>4.534687610267789</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78072519474607</v>
+        <v>32.62230154981415</v>
       </c>
       <c r="O6" t="n">
-        <v>5.637439595662739</v>
+        <v>5.711593608601206</v>
       </c>
       <c r="P6" t="n">
-        <v>326.7361547362659</v>
+        <v>326.8889612658306</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16862,7 +16936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G416"/>
+  <dimension ref="A1:G418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32233,6 +32307,80 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-45.12200188491049,170.98052462961994</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-45.12227148694704,170.97964905244902</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-45.12278649177525,170.97899672661313</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-45.12321672550214,170.97830272670282</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-45.12373365366577,170.97775272725718</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-45.12200141860461,170.98052424514552</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-45.12226899551284,170.97964654385726</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-45.12277630604166,170.9789836412916</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-45.12320113655534,170.9782807043522</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-45.123718985548564,170.9777312092159</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11710,6 +11710,60 @@
         <v>301.06</v>
       </c>
       <c r="G418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>304.07</v>
+      </c>
+      <c r="C419" t="n">
+        <v>294.66</v>
+      </c>
+      <c r="D419" t="n">
+        <v>299.86</v>
+      </c>
+      <c r="E419" t="n">
+        <v>293.84</v>
+      </c>
+      <c r="F419" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>305.02</v>
+      </c>
+      <c r="C420" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="D420" t="n">
+        <v>298.77</v>
+      </c>
+      <c r="E420" t="n">
+        <v>293.29</v>
+      </c>
+      <c r="F420" t="n">
+        <v>299.7</v>
+      </c>
+      <c r="G420" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11726,7 +11780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16389,6 +16443,26 @@
       </c>
       <c r="B466" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -16557,28 +16631,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2747091125495743</v>
+        <v>-0.2700337690256965</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01776438337765773</v>
+        <v>0.01733203091793689</v>
       </c>
       <c r="M2" t="n">
-        <v>12.72912104236963</v>
+        <v>12.69019723102259</v>
       </c>
       <c r="N2" t="n">
-        <v>217.3332620849215</v>
+        <v>216.4006600209809</v>
       </c>
       <c r="O2" t="n">
-        <v>14.74222717519037</v>
+        <v>14.71056287233704</v>
       </c>
       <c r="P2" t="n">
-        <v>306.9115585740059</v>
+        <v>306.8589840718907</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16639,28 +16713,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5553773353043716</v>
+        <v>-0.5508801609408868</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05714411402490593</v>
+        <v>0.05677398627022279</v>
       </c>
       <c r="M3" t="n">
-        <v>13.53290111815487</v>
+        <v>13.49024800643373</v>
       </c>
       <c r="N3" t="n">
-        <v>265.9823960488398</v>
+        <v>264.8180324596844</v>
       </c>
       <c r="O3" t="n">
-        <v>16.30896673762136</v>
+        <v>16.27323054773343</v>
       </c>
       <c r="P3" t="n">
-        <v>304.841727645492</v>
+        <v>304.7913748832086</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16721,28 +16795,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7202455384361239</v>
+        <v>-0.726636757798502</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4215106244729381</v>
+        <v>0.4267755682507083</v>
       </c>
       <c r="M4" t="n">
-        <v>4.895947319141836</v>
+        <v>4.907845674626402</v>
       </c>
       <c r="N4" t="n">
-        <v>37.16849336266782</v>
+        <v>37.21010491377242</v>
       </c>
       <c r="O4" t="n">
-        <v>6.096596867324247</v>
+        <v>6.100008599483481</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2819191881263</v>
+        <v>325.3534753027204</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16799,28 +16873,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5442023444277596</v>
+        <v>-0.5555320431868498</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.334205003140432</v>
+        <v>0.340668097708348</v>
       </c>
       <c r="M5" t="n">
-        <v>4.575018439258449</v>
+        <v>4.626850989383954</v>
       </c>
       <c r="N5" t="n">
-        <v>30.80174629335026</v>
+        <v>31.33948658582595</v>
       </c>
       <c r="O5" t="n">
-        <v>5.549932098084648</v>
+        <v>5.598168145547787</v>
       </c>
       <c r="P5" t="n">
-        <v>320.1040906159649</v>
+        <v>320.2309278392075</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16877,28 +16951,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3924073235028762</v>
+        <v>-0.4077613732059455</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1977060903401522</v>
+        <v>0.2055195569168751</v>
       </c>
       <c r="M6" t="n">
-        <v>4.534687610267789</v>
+        <v>4.598686226916222</v>
       </c>
       <c r="N6" t="n">
-        <v>32.62230154981415</v>
+        <v>33.72432352822419</v>
       </c>
       <c r="O6" t="n">
-        <v>5.711593608601206</v>
+        <v>5.807264720005812</v>
       </c>
       <c r="P6" t="n">
-        <v>326.8889612658306</v>
+        <v>327.0608521076719</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16936,7 +17010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32381,6 +32455,80 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-45.12202310182632,170.98054212321327</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-45.12229691422837,170.9796746548536</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-45.12278376226509,170.97899322008863</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-45.12320438160174,170.9782852885956</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-45.12371549016687,170.9777260815141</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-45.12203048500157,170.98054821073043</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-45.12229977204928,170.9796775323587</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-45.122776505761934,170.9789838978665</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-45.12320088204188,170.9782803448037</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-45.123710496764055,170.97771875622686</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>305.02</v>
+        <v>302.37</v>
       </c>
       <c r="C420" t="n">
-        <v>295.05</v>
+        <v>293.38</v>
       </c>
       <c r="D420" t="n">
         <v>298.77</v>
@@ -11764,6 +11764,114 @@
         <v>299.7</v>
       </c>
       <c r="G420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>300.09</v>
+      </c>
+      <c r="C421" t="n">
+        <v>290.79</v>
+      </c>
+      <c r="D421" t="n">
+        <v>298.37</v>
+      </c>
+      <c r="E421" t="n">
+        <v>293.19</v>
+      </c>
+      <c r="F421" t="n">
+        <v>299.92</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>297.57</v>
+      </c>
+      <c r="C422" t="n">
+        <v>289.69</v>
+      </c>
+      <c r="D422" t="n">
+        <v>297.72</v>
+      </c>
+      <c r="E422" t="n">
+        <v>292.73</v>
+      </c>
+      <c r="F422" t="n">
+        <v>301.53</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>296.04</v>
+      </c>
+      <c r="C423" t="n">
+        <v>287.25</v>
+      </c>
+      <c r="D423" t="n">
+        <v>297.09</v>
+      </c>
+      <c r="E423" t="n">
+        <v>292.55</v>
+      </c>
+      <c r="F423" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>293.53</v>
+      </c>
+      <c r="C424" t="n">
+        <v>281.43</v>
+      </c>
+      <c r="D424" t="n">
+        <v>297.13</v>
+      </c>
+      <c r="E424" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="F424" t="n">
+        <v>302.92</v>
+      </c>
+      <c r="G424" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11780,7 +11888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16463,6 +16571,56 @@
       </c>
       <c r="B468" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -16631,28 +16789,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2700337690256965</v>
+        <v>-0.2765414259987542</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01733203091793689</v>
+        <v>0.01850396945631816</v>
       </c>
       <c r="M2" t="n">
-        <v>12.69019723102259</v>
+        <v>12.59300285978656</v>
       </c>
       <c r="N2" t="n">
-        <v>216.4006600209809</v>
+        <v>214.4069273508589</v>
       </c>
       <c r="O2" t="n">
-        <v>14.71056287233704</v>
+        <v>14.64264072327321</v>
       </c>
       <c r="P2" t="n">
-        <v>306.8589840718907</v>
+        <v>306.9324543787619</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16713,28 +16871,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5508801609408868</v>
+        <v>-0.5568163372119888</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05677398627022279</v>
+        <v>0.05896234638836662</v>
       </c>
       <c r="M3" t="n">
-        <v>13.49024800643373</v>
+        <v>13.38877095907944</v>
       </c>
       <c r="N3" t="n">
-        <v>264.8180324596844</v>
+        <v>262.4702256316978</v>
       </c>
       <c r="O3" t="n">
-        <v>16.27323054773343</v>
+        <v>16.20093286300816</v>
       </c>
       <c r="P3" t="n">
-        <v>304.7913748832086</v>
+        <v>304.8581455528815</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16795,28 +16953,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.726636757798502</v>
+        <v>-0.7420671037641944</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K4" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4267755682507083</v>
+        <v>0.4375593532224836</v>
       </c>
       <c r="M4" t="n">
-        <v>4.907845674626402</v>
+        <v>4.946192975618671</v>
       </c>
       <c r="N4" t="n">
-        <v>37.21010491377242</v>
+        <v>37.50625246617633</v>
       </c>
       <c r="O4" t="n">
-        <v>6.100008599483481</v>
+        <v>6.124234847405537</v>
       </c>
       <c r="P4" t="n">
-        <v>325.3534753027204</v>
+        <v>325.5268848331668</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16873,28 +17031,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5555320431868498</v>
+        <v>-0.5784435500147789</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K5" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L5" t="n">
-        <v>0.340668097708348</v>
+        <v>0.3531970522769174</v>
       </c>
       <c r="M5" t="n">
-        <v>4.626850989383954</v>
+        <v>4.732340215373548</v>
       </c>
       <c r="N5" t="n">
-        <v>31.33948658582595</v>
+        <v>32.46792036459177</v>
       </c>
       <c r="O5" t="n">
-        <v>5.598168145547787</v>
+        <v>5.698062860709047</v>
       </c>
       <c r="P5" t="n">
-        <v>320.2309278392075</v>
+        <v>320.4883954613601</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16951,28 +17109,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4077613732059455</v>
+        <v>-0.4349319032975846</v>
       </c>
       <c r="J6" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K6" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2055195569168751</v>
+        <v>0.2205748422859585</v>
       </c>
       <c r="M6" t="n">
-        <v>4.598686226916222</v>
+        <v>4.710944584976691</v>
       </c>
       <c r="N6" t="n">
-        <v>33.72432352822419</v>
+        <v>35.41918463147518</v>
       </c>
       <c r="O6" t="n">
-        <v>5.807264720005812</v>
+        <v>5.951401904717508</v>
       </c>
       <c r="P6" t="n">
-        <v>327.0608521076719</v>
+        <v>327.3661595972643</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17010,7 +17168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32500,12 +32658,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>-45.12203048500157,170.98054821073043</t>
+          <t>-45.12200988982776,170.98053122976538</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>-45.12229977204928,170.9796775323587</t>
+          <t>-45.12228753471314,170.9796652107363</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -32524,6 +32682,154 @@
         </is>
       </c>
       <c r="G420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-45.1219921702046,170.98051661973716</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-45.122268555847974,170.9796461011646</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-45.12277384282482,170.97898047686814</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-45.123200245758255,170.97827944593251</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-45.12371186994988,170.97772077068072</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-45.12197258535591,170.98050047182164</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-45.12226049532518,170.9796379851341</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-45.122769515551795,170.97897491774648</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-45.12319731885345,170.97827531112526</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-45.12372191917231,170.97773551282327</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-45.12196069455386,170.98049066773538</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-45.12224261561811,170.9796199823109</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-45.12276532142538,170.97896952967554</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-45.12319617354284,170.97827369315735</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-45.123720421151695,170.9777333152365</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-45.121941187419374,170.9804745839163</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-45.12219996810922,170.97957704119568</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-45.12276558771913,170.97896987177526</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-45.12320126381206,170.9782808841264</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-45.12373059520761,170.97774824051575</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11872,6 +11872,60 @@
         <v>302.92</v>
       </c>
       <c r="G424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>289.92</v>
+      </c>
+      <c r="C425" t="n">
+        <v>277.01</v>
+      </c>
+      <c r="D425" t="n">
+        <v>293.59</v>
+      </c>
+      <c r="E425" t="n">
+        <v>291.77</v>
+      </c>
+      <c r="F425" t="n">
+        <v>302.58</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="C426" t="n">
+        <v>270.91</v>
+      </c>
+      <c r="D426" t="n">
+        <v>287.28</v>
+      </c>
+      <c r="E426" t="n">
+        <v>289.91</v>
+      </c>
+      <c r="F426" t="n">
+        <v>302</v>
+      </c>
+      <c r="G426" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11888,7 +11942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B473"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16621,6 +16675,26 @@
       </c>
       <c r="B473" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -16789,28 +16863,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2765414259987542</v>
+        <v>-0.2868509764829495</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01850396945631816</v>
+        <v>0.02001462256050024</v>
       </c>
       <c r="M2" t="n">
-        <v>12.59300285978656</v>
+        <v>12.58770753984065</v>
       </c>
       <c r="N2" t="n">
-        <v>214.4069273508589</v>
+        <v>213.9822138629726</v>
       </c>
       <c r="O2" t="n">
-        <v>14.64264072327321</v>
+        <v>14.62813090804743</v>
       </c>
       <c r="P2" t="n">
-        <v>306.9324543787619</v>
+        <v>307.04938623308</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16871,28 +16945,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5568163372119888</v>
+        <v>-0.5714692114593234</v>
       </c>
       <c r="J3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05896234638836662</v>
+        <v>0.06219637346168982</v>
       </c>
       <c r="M3" t="n">
-        <v>13.38877095907944</v>
+        <v>13.40125441890557</v>
       </c>
       <c r="N3" t="n">
-        <v>262.4702256316978</v>
+        <v>262.4629294166427</v>
       </c>
       <c r="O3" t="n">
-        <v>16.20093286300816</v>
+        <v>16.20070768258729</v>
       </c>
       <c r="P3" t="n">
-        <v>304.8581455528815</v>
+        <v>305.0236343800757</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16953,28 +17027,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7420671037641944</v>
+        <v>-0.7560112245777451</v>
       </c>
       <c r="J4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4375593532224836</v>
+        <v>0.4418195489494136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.946192975618671</v>
+        <v>5.00099781221728</v>
       </c>
       <c r="N4" t="n">
-        <v>37.50625246617633</v>
+        <v>38.44899700247201</v>
       </c>
       <c r="O4" t="n">
-        <v>6.124234847405537</v>
+        <v>6.200725522265278</v>
       </c>
       <c r="P4" t="n">
-        <v>325.5268848331668</v>
+        <v>325.6843507194296</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17031,28 +17105,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5784435500147789</v>
+        <v>-0.5914161675337255</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3531970522769174</v>
+        <v>0.3590453573390532</v>
       </c>
       <c r="M5" t="n">
-        <v>4.732340215373548</v>
+        <v>4.795388323418712</v>
       </c>
       <c r="N5" t="n">
-        <v>32.46792036459177</v>
+        <v>33.2478220272971</v>
       </c>
       <c r="O5" t="n">
-        <v>5.698062860709047</v>
+        <v>5.766092440058267</v>
       </c>
       <c r="P5" t="n">
-        <v>320.4883954613601</v>
+        <v>320.6348805512154</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17109,28 +17183,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4349319032975846</v>
+        <v>-0.4472366990281428</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2205748422859585</v>
+        <v>0.2278732392499205</v>
       </c>
       <c r="M6" t="n">
-        <v>4.710944584976691</v>
+        <v>4.762343844582756</v>
       </c>
       <c r="N6" t="n">
-        <v>35.41918463147518</v>
+        <v>36.08851229224359</v>
       </c>
       <c r="O6" t="n">
-        <v>5.951401904717508</v>
+        <v>6.007371496107393</v>
       </c>
       <c r="P6" t="n">
-        <v>327.3661595972643</v>
+        <v>327.50510081099</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17168,7 +17242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32835,6 +32909,80 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-45.121913131337756,170.98045145143055</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-45.122167579441026,170.97954442960074</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-45.122742020718675,170.9789395959624</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-45.12319121052994,170.97826668196373</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-45.12372847301205,170.97774512726687</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-45.12188888341876,170.98043145882932</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-45.1221228801333,170.97949942270856</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-45.12270001285416,170.97888562981532</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-45.12317937565133,170.9782499629685</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-45.1237248527959,170.9777398164311</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
